--- a/rozvrh státní závěrečné zkousky.xlsx
+++ b/rozvrh státní závěrečné zkousky.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bruli\Desktop\bc-szz\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bruli\Desktop\bc-szz\bc-szz\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17A9A64A-9C90-498A-8665-DC65B74C7624}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87E690B9-B690-4681-9FE7-4067BAB0C147}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="43095" yWindow="0" windowWidth="14610" windowHeight="15585" activeTab="2" xr2:uid="{E4BE6AF0-EAEA-4BDD-8135-F0B689BF69C4}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E4BE6AF0-EAEA-4BDD-8135-F0B689BF69C4}"/>
   </bookViews>
   <sheets>
     <sheet name="SZZTP" sheetId="1" r:id="rId1"/>
@@ -697,7 +697,7 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -737,9 +737,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="2"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="2" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -747,13 +744,13 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -1247,31 +1244,31 @@
       <c r="B8" s="6">
         <v>1</v>
       </c>
-      <c r="C8" s="28" t="s">
+      <c r="C8" s="25" t="s">
         <v>5</v>
       </c>
-      <c r="D8" s="28"/>
-      <c r="E8" s="28"/>
-      <c r="F8" s="28"/>
-      <c r="G8" s="28"/>
-      <c r="H8" s="28"/>
-      <c r="I8" s="28"/>
-      <c r="J8" s="28"/>
-      <c r="K8" s="28"/>
-      <c r="L8" s="28"/>
-      <c r="M8" s="28"/>
-      <c r="N8" s="28"/>
-      <c r="O8" s="28"/>
-      <c r="P8" s="28"/>
-      <c r="Q8" s="28"/>
-      <c r="R8" s="28"/>
-      <c r="S8" s="28"/>
-      <c r="T8" s="28"/>
-      <c r="U8" s="28"/>
-      <c r="V8" s="28"/>
-      <c r="W8" s="28"/>
-      <c r="X8" s="28"/>
-      <c r="Y8" s="28"/>
+      <c r="D8" s="25"/>
+      <c r="E8" s="25"/>
+      <c r="F8" s="25"/>
+      <c r="G8" s="25"/>
+      <c r="H8" s="25"/>
+      <c r="I8" s="25"/>
+      <c r="J8" s="25"/>
+      <c r="K8" s="25"/>
+      <c r="L8" s="25"/>
+      <c r="M8" s="25"/>
+      <c r="N8" s="25"/>
+      <c r="O8" s="25"/>
+      <c r="P8" s="25"/>
+      <c r="Q8" s="25"/>
+      <c r="R8" s="25"/>
+      <c r="S8" s="25"/>
+      <c r="T8" s="25"/>
+      <c r="U8" s="25"/>
+      <c r="V8" s="25"/>
+      <c r="W8" s="25"/>
+      <c r="X8" s="25"/>
+      <c r="Y8" s="25"/>
       <c r="Z8" s="7"/>
       <c r="AA8" s="7"/>
     </row>
@@ -1282,31 +1279,31 @@
       <c r="B9" s="6">
         <v>2</v>
       </c>
-      <c r="C9" s="28" t="s">
+      <c r="C9" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="D9" s="28"/>
-      <c r="E9" s="28"/>
-      <c r="F9" s="28"/>
-      <c r="G9" s="28"/>
-      <c r="H9" s="28"/>
-      <c r="I9" s="28"/>
-      <c r="J9" s="28"/>
-      <c r="K9" s="28"/>
-      <c r="L9" s="28"/>
-      <c r="M9" s="28"/>
-      <c r="N9" s="28"/>
-      <c r="O9" s="28"/>
-      <c r="P9" s="28"/>
-      <c r="Q9" s="28"/>
-      <c r="R9" s="28"/>
-      <c r="S9" s="28"/>
-      <c r="T9" s="28"/>
-      <c r="U9" s="28"/>
-      <c r="V9" s="28"/>
-      <c r="W9" s="28"/>
-      <c r="X9" s="28"/>
-      <c r="Y9" s="28"/>
+      <c r="D9" s="25"/>
+      <c r="E9" s="25"/>
+      <c r="F9" s="25"/>
+      <c r="G9" s="25"/>
+      <c r="H9" s="25"/>
+      <c r="I9" s="25"/>
+      <c r="J9" s="25"/>
+      <c r="K9" s="25"/>
+      <c r="L9" s="25"/>
+      <c r="M9" s="25"/>
+      <c r="N9" s="25"/>
+      <c r="O9" s="25"/>
+      <c r="P9" s="25"/>
+      <c r="Q9" s="25"/>
+      <c r="R9" s="25"/>
+      <c r="S9" s="25"/>
+      <c r="T9" s="25"/>
+      <c r="U9" s="25"/>
+      <c r="V9" s="25"/>
+      <c r="W9" s="25"/>
+      <c r="X9" s="25"/>
+      <c r="Y9" s="25"/>
       <c r="Z9" s="7"/>
     </row>
     <row r="10" spans="1:27" ht="42.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -1316,31 +1313,31 @@
       <c r="B10" s="6">
         <v>3</v>
       </c>
-      <c r="C10" s="28" t="s">
+      <c r="C10" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="D10" s="28"/>
-      <c r="E10" s="28"/>
-      <c r="F10" s="28"/>
-      <c r="G10" s="28"/>
-      <c r="H10" s="28"/>
-      <c r="I10" s="28"/>
-      <c r="J10" s="28"/>
-      <c r="K10" s="28"/>
-      <c r="L10" s="28"/>
-      <c r="M10" s="28"/>
-      <c r="N10" s="28"/>
-      <c r="O10" s="28"/>
-      <c r="P10" s="28"/>
-      <c r="Q10" s="28"/>
-      <c r="R10" s="28"/>
-      <c r="S10" s="28"/>
-      <c r="T10" s="28"/>
-      <c r="U10" s="28"/>
-      <c r="V10" s="28"/>
-      <c r="W10" s="28"/>
-      <c r="X10" s="28"/>
-      <c r="Y10" s="28"/>
+      <c r="D10" s="25"/>
+      <c r="E10" s="25"/>
+      <c r="F10" s="25"/>
+      <c r="G10" s="25"/>
+      <c r="H10" s="25"/>
+      <c r="I10" s="25"/>
+      <c r="J10" s="25"/>
+      <c r="K10" s="25"/>
+      <c r="L10" s="25"/>
+      <c r="M10" s="25"/>
+      <c r="N10" s="25"/>
+      <c r="O10" s="25"/>
+      <c r="P10" s="25"/>
+      <c r="Q10" s="25"/>
+      <c r="R10" s="25"/>
+      <c r="S10" s="25"/>
+      <c r="T10" s="25"/>
+      <c r="U10" s="25"/>
+      <c r="V10" s="25"/>
+      <c r="W10" s="25"/>
+      <c r="X10" s="25"/>
+      <c r="Y10" s="25"/>
       <c r="Z10" s="7"/>
     </row>
     <row r="11" spans="1:27" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -1350,75 +1347,584 @@
       <c r="B11" s="6">
         <v>4</v>
       </c>
-      <c r="C11" s="28" t="s">
+      <c r="C11" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="D11" s="28"/>
-      <c r="E11" s="28"/>
-      <c r="F11" s="28"/>
-      <c r="G11" s="28"/>
-      <c r="H11" s="28"/>
-      <c r="I11" s="28"/>
-      <c r="J11" s="28"/>
-      <c r="K11" s="28"/>
-      <c r="L11" s="28"/>
-      <c r="M11" s="28"/>
-      <c r="N11" s="28"/>
-      <c r="O11" s="28"/>
-      <c r="P11" s="28"/>
-      <c r="Q11" s="28"/>
-      <c r="R11" s="28"/>
-      <c r="S11" s="28"/>
-      <c r="T11" s="28"/>
-      <c r="U11" s="28"/>
-      <c r="V11" s="28"/>
-      <c r="W11" s="28"/>
-      <c r="X11" s="28"/>
-      <c r="Y11" s="28"/>
+      <c r="D11" s="25"/>
+      <c r="E11" s="25"/>
+      <c r="F11" s="25"/>
+      <c r="G11" s="25"/>
+      <c r="H11" s="25"/>
+      <c r="I11" s="25"/>
+      <c r="J11" s="25"/>
+      <c r="K11" s="25"/>
+      <c r="L11" s="25"/>
+      <c r="M11" s="25"/>
+      <c r="N11" s="25"/>
+      <c r="O11" s="25"/>
+      <c r="P11" s="25"/>
+      <c r="Q11" s="25"/>
+      <c r="R11" s="25"/>
+      <c r="S11" s="25"/>
+      <c r="T11" s="25"/>
+      <c r="U11" s="25"/>
+      <c r="V11" s="25"/>
+      <c r="W11" s="25"/>
+      <c r="X11" s="25"/>
+      <c r="Y11" s="25"/>
     </row>
     <row r="12" spans="1:27" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="B12" s="9">
+      <c r="B12" s="6">
         <v>5</v>
       </c>
-      <c r="C12" s="28" t="s">
+      <c r="C12" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="D12" s="28"/>
-      <c r="E12" s="28"/>
-      <c r="F12" s="28"/>
-      <c r="G12" s="28"/>
-      <c r="H12" s="28"/>
-      <c r="I12" s="28"/>
-      <c r="J12" s="28"/>
-      <c r="K12" s="28"/>
-      <c r="L12" s="28"/>
-      <c r="M12" s="28"/>
-      <c r="N12" s="28"/>
-      <c r="O12" s="28"/>
-      <c r="P12" s="28"/>
-      <c r="Q12" s="28"/>
-      <c r="R12" s="28"/>
-      <c r="S12" s="28"/>
-      <c r="T12" s="28"/>
-      <c r="U12" s="28"/>
-      <c r="V12" s="28"/>
-      <c r="W12" s="28"/>
-      <c r="X12" s="28"/>
-      <c r="Y12" s="28"/>
+      <c r="D12" s="25"/>
+      <c r="E12" s="25"/>
+      <c r="F12" s="25"/>
+      <c r="G12" s="25"/>
+      <c r="H12" s="25"/>
+      <c r="I12" s="25"/>
+      <c r="J12" s="25"/>
+      <c r="K12" s="25"/>
+      <c r="L12" s="25"/>
+      <c r="M12" s="25"/>
+      <c r="N12" s="25"/>
+      <c r="O12" s="25"/>
+      <c r="P12" s="25"/>
+      <c r="Q12" s="25"/>
+      <c r="R12" s="25"/>
+      <c r="S12" s="25"/>
+      <c r="T12" s="25"/>
+      <c r="U12" s="25"/>
+      <c r="V12" s="25"/>
+      <c r="W12" s="25"/>
+      <c r="X12" s="25"/>
+      <c r="Y12" s="25"/>
       <c r="Z12" s="7"/>
     </row>
     <row r="13" spans="1:27" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="B13" s="9">
+      <c r="B13" s="6">
         <v>6</v>
       </c>
+      <c r="C13" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="D13" s="25"/>
+      <c r="E13" s="25"/>
+      <c r="F13" s="25"/>
+      <c r="G13" s="25"/>
+      <c r="H13" s="25"/>
+      <c r="I13" s="25"/>
+      <c r="J13" s="25"/>
+      <c r="K13" s="25"/>
+      <c r="L13" s="25"/>
+      <c r="M13" s="25"/>
+      <c r="N13" s="25"/>
+      <c r="O13" s="25"/>
+      <c r="P13" s="25"/>
+      <c r="Q13" s="25"/>
+      <c r="R13" s="25"/>
+      <c r="S13" s="25"/>
+      <c r="T13" s="25"/>
+      <c r="U13" s="25"/>
+      <c r="V13" s="25"/>
+      <c r="W13" s="25"/>
+      <c r="X13" s="25"/>
+      <c r="Y13" s="25"/>
+      <c r="Z13" s="7"/>
+    </row>
+    <row r="14" spans="1:27" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="B14" s="6">
+        <v>7</v>
+      </c>
+      <c r="C14" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="D14" s="25"/>
+      <c r="E14" s="25"/>
+      <c r="F14" s="25"/>
+      <c r="G14" s="25"/>
+      <c r="H14" s="25"/>
+      <c r="I14" s="25"/>
+      <c r="J14" s="25"/>
+      <c r="K14" s="25"/>
+      <c r="L14" s="25"/>
+      <c r="M14" s="25"/>
+      <c r="N14" s="25"/>
+      <c r="O14" s="25"/>
+      <c r="P14" s="25"/>
+      <c r="Q14" s="25"/>
+      <c r="R14" s="25"/>
+      <c r="S14" s="25"/>
+      <c r="T14" s="25"/>
+      <c r="U14" s="25"/>
+      <c r="V14" s="25"/>
+      <c r="W14" s="25"/>
+      <c r="X14" s="25"/>
+      <c r="Y14" s="25"/>
+      <c r="Z14" s="7"/>
+    </row>
+    <row r="15" spans="1:27" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="B15" s="6">
+        <v>8</v>
+      </c>
+      <c r="C15" s="25" t="s">
+        <v>12</v>
+      </c>
+      <c r="D15" s="25"/>
+      <c r="E15" s="25"/>
+      <c r="F15" s="25"/>
+      <c r="G15" s="25"/>
+      <c r="H15" s="25"/>
+      <c r="I15" s="25"/>
+      <c r="J15" s="25"/>
+      <c r="K15" s="25"/>
+      <c r="L15" s="25"/>
+      <c r="M15" s="25"/>
+      <c r="N15" s="25"/>
+      <c r="O15" s="25"/>
+      <c r="P15" s="25"/>
+      <c r="Q15" s="25"/>
+      <c r="R15" s="25"/>
+      <c r="S15" s="25"/>
+      <c r="T15" s="25"/>
+      <c r="U15" s="25"/>
+      <c r="V15" s="25"/>
+      <c r="W15" s="25"/>
+      <c r="X15" s="25"/>
+      <c r="Y15" s="25"/>
+      <c r="Z15" s="7"/>
+    </row>
+    <row r="16" spans="1:27" ht="48" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="B16" s="6">
+        <v>9</v>
+      </c>
+      <c r="C16" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="D16" s="25"/>
+      <c r="E16" s="25"/>
+      <c r="F16" s="25"/>
+      <c r="G16" s="25"/>
+      <c r="H16" s="25"/>
+      <c r="I16" s="25"/>
+      <c r="J16" s="25"/>
+      <c r="K16" s="25"/>
+      <c r="L16" s="25"/>
+      <c r="M16" s="25"/>
+      <c r="N16" s="25"/>
+      <c r="O16" s="25"/>
+      <c r="P16" s="25"/>
+      <c r="Q16" s="25"/>
+      <c r="R16" s="25"/>
+      <c r="S16" s="25"/>
+      <c r="T16" s="25"/>
+      <c r="U16" s="25"/>
+      <c r="V16" s="25"/>
+      <c r="W16" s="25"/>
+      <c r="X16" s="25"/>
+      <c r="Y16" s="25"/>
+    </row>
+    <row r="17" spans="1:25" ht="57.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="B17" s="6">
+        <v>10</v>
+      </c>
+      <c r="C17" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="D17" s="25"/>
+      <c r="E17" s="25"/>
+      <c r="F17" s="25"/>
+      <c r="G17" s="25"/>
+      <c r="H17" s="25"/>
+      <c r="I17" s="25"/>
+      <c r="J17" s="25"/>
+      <c r="K17" s="25"/>
+      <c r="L17" s="25"/>
+      <c r="M17" s="25"/>
+      <c r="N17" s="25"/>
+      <c r="O17" s="25"/>
+      <c r="P17" s="25"/>
+      <c r="Q17" s="25"/>
+      <c r="R17" s="25"/>
+      <c r="S17" s="25"/>
+      <c r="T17" s="25"/>
+      <c r="U17" s="25"/>
+      <c r="V17" s="25"/>
+      <c r="W17" s="25"/>
+      <c r="X17" s="25"/>
+      <c r="Y17" s="25"/>
+    </row>
+    <row r="18" spans="1:25" ht="48" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="B18" s="9">
+        <v>11</v>
+      </c>
+      <c r="C18" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="D18" s="25"/>
+      <c r="E18" s="25"/>
+      <c r="F18" s="25"/>
+      <c r="G18" s="25"/>
+      <c r="H18" s="25"/>
+      <c r="I18" s="25"/>
+      <c r="J18" s="25"/>
+      <c r="K18" s="25"/>
+      <c r="L18" s="25"/>
+      <c r="M18" s="25"/>
+      <c r="N18" s="25"/>
+      <c r="O18" s="25"/>
+      <c r="P18" s="25"/>
+      <c r="Q18" s="25"/>
+      <c r="R18" s="25"/>
+      <c r="S18" s="25"/>
+      <c r="T18" s="25"/>
+      <c r="U18" s="25"/>
+      <c r="V18" s="25"/>
+      <c r="W18" s="25"/>
+      <c r="X18" s="25"/>
+      <c r="Y18" s="25"/>
+    </row>
+    <row r="19" spans="1:25" ht="55.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="B19" s="9">
+        <v>12</v>
+      </c>
+      <c r="C19" s="25" t="s">
+        <v>16</v>
+      </c>
+      <c r="D19" s="25"/>
+      <c r="E19" s="25"/>
+      <c r="F19" s="25"/>
+      <c r="G19" s="25"/>
+      <c r="H19" s="25"/>
+      <c r="I19" s="25"/>
+      <c r="J19" s="25"/>
+      <c r="K19" s="25"/>
+      <c r="L19" s="25"/>
+      <c r="M19" s="25"/>
+      <c r="N19" s="25"/>
+      <c r="O19" s="25"/>
+      <c r="P19" s="25"/>
+      <c r="Q19" s="25"/>
+      <c r="R19" s="25"/>
+      <c r="S19" s="25"/>
+      <c r="T19" s="25"/>
+      <c r="U19" s="25"/>
+      <c r="V19" s="25"/>
+      <c r="W19" s="25"/>
+      <c r="X19" s="25"/>
+      <c r="Y19" s="25"/>
+    </row>
+  </sheetData>
+  <mergeCells count="16">
+    <mergeCell ref="A4:Z4"/>
+    <mergeCell ref="A5:Z5"/>
+    <mergeCell ref="A1:Z1"/>
+    <mergeCell ref="A3:Z3"/>
+    <mergeCell ref="C16:Y16"/>
+    <mergeCell ref="C17:Y17"/>
+    <mergeCell ref="C18:Y18"/>
+    <mergeCell ref="C19:Y19"/>
+    <mergeCell ref="C8:Y8"/>
+    <mergeCell ref="C9:Y9"/>
+    <mergeCell ref="C10:Y10"/>
+    <mergeCell ref="C11:Y11"/>
+    <mergeCell ref="C12:Y12"/>
+    <mergeCell ref="C13:Y13"/>
+    <mergeCell ref="C14:Y14"/>
+    <mergeCell ref="C15:Y15"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E579CA94-23C4-4A08-ACCB-1F78709F95AA}">
+  <dimension ref="A1:Z32"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="35.7109375" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" customWidth="1"/>
+    <col min="3" max="3" width="14.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:26" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A1" s="31" t="s">
+        <v>17</v>
+      </c>
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="31"/>
+      <c r="H1" s="31"/>
+      <c r="I1" s="31"/>
+      <c r="J1" s="31"/>
+      <c r="K1" s="31"/>
+      <c r="L1" s="31"/>
+      <c r="M1" s="31"/>
+      <c r="N1" s="31"/>
+      <c r="O1" s="31"/>
+      <c r="P1" s="31"/>
+      <c r="Q1" s="31"/>
+      <c r="R1" s="31"/>
+      <c r="S1" s="31"/>
+      <c r="T1" s="31"/>
+      <c r="U1" s="31"/>
+      <c r="V1" s="31"/>
+      <c r="W1" s="31"/>
+      <c r="X1" s="31"/>
+      <c r="Y1" s="31"/>
+      <c r="Z1" s="31"/>
+    </row>
+    <row r="3" spans="1:26" ht="52.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="32" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" s="32"/>
+      <c r="C3" s="32"/>
+      <c r="D3" s="32"/>
+      <c r="E3" s="32"/>
+      <c r="F3" s="32"/>
+      <c r="G3" s="32"/>
+      <c r="H3" s="32"/>
+      <c r="I3" s="32"/>
+      <c r="J3" s="32"/>
+      <c r="K3" s="32"/>
+      <c r="L3" s="32"/>
+      <c r="M3" s="32"/>
+      <c r="N3" s="32"/>
+      <c r="O3" s="32"/>
+      <c r="P3" s="32"/>
+      <c r="Q3" s="32"/>
+      <c r="R3" s="32"/>
+      <c r="S3" s="32"/>
+      <c r="T3" s="32"/>
+      <c r="U3" s="32"/>
+      <c r="V3" s="32"/>
+      <c r="W3" s="32"/>
+      <c r="X3" s="32"/>
+      <c r="Y3" s="32"/>
+      <c r="Z3" s="32"/>
+    </row>
+    <row r="4" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" s="32"/>
+      <c r="C4" s="32"/>
+      <c r="D4" s="32"/>
+      <c r="E4" s="32"/>
+      <c r="F4" s="32"/>
+      <c r="G4" s="32"/>
+      <c r="H4" s="32"/>
+      <c r="I4" s="32"/>
+      <c r="J4" s="32"/>
+      <c r="K4" s="32"/>
+      <c r="L4" s="32"/>
+      <c r="M4" s="32"/>
+      <c r="N4" s="32"/>
+      <c r="O4" s="32"/>
+      <c r="P4" s="32"/>
+      <c r="Q4" s="32"/>
+      <c r="R4" s="32"/>
+      <c r="S4" s="32"/>
+      <c r="T4" s="32"/>
+      <c r="U4" s="32"/>
+      <c r="V4" s="32"/>
+      <c r="W4" s="32"/>
+      <c r="X4" s="32"/>
+      <c r="Y4" s="32"/>
+      <c r="Z4" s="32"/>
+    </row>
+    <row r="5" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" s="32"/>
+      <c r="C5" s="32"/>
+      <c r="D5" s="32"/>
+      <c r="E5" s="32"/>
+      <c r="F5" s="32"/>
+      <c r="G5" s="32"/>
+      <c r="H5" s="32"/>
+      <c r="I5" s="32"/>
+      <c r="J5" s="32"/>
+      <c r="K5" s="32"/>
+      <c r="L5" s="32"/>
+      <c r="M5" s="32"/>
+      <c r="N5" s="32"/>
+      <c r="O5" s="32"/>
+      <c r="P5" s="32"/>
+      <c r="Q5" s="32"/>
+      <c r="R5" s="32"/>
+      <c r="S5" s="32"/>
+      <c r="T5" s="32"/>
+      <c r="U5" s="32"/>
+      <c r="V5" s="32"/>
+      <c r="W5" s="32"/>
+      <c r="X5" s="32"/>
+      <c r="Y5" s="32"/>
+      <c r="Z5" s="32"/>
+    </row>
+    <row r="7" spans="1:26" ht="59.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" s="30" t="s">
+        <v>25</v>
+      </c>
+      <c r="D7" s="30"/>
+      <c r="E7" s="30"/>
+      <c r="F7" s="30"/>
+      <c r="G7" s="30"/>
+      <c r="H7" s="30"/>
+      <c r="I7" s="30"/>
+      <c r="J7" s="30"/>
+      <c r="K7" s="30"/>
+      <c r="L7" s="30"/>
+      <c r="M7" s="30"/>
+      <c r="N7" s="30"/>
+      <c r="O7" s="30"/>
+      <c r="P7" s="30"/>
+      <c r="Q7" s="30"/>
+      <c r="R7" s="30"/>
+      <c r="S7" s="30"/>
+      <c r="T7" s="30"/>
+      <c r="U7" s="30"/>
+      <c r="V7" s="30"/>
+      <c r="W7" s="30"/>
+      <c r="X7" s="12"/>
+      <c r="Y7" s="12"/>
+      <c r="Z7" s="12"/>
+    </row>
+    <row r="8" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8" s="30" t="s">
+        <v>27</v>
+      </c>
+      <c r="D8" s="30"/>
+      <c r="E8" s="30"/>
+      <c r="F8" s="30"/>
+      <c r="G8" s="30"/>
+      <c r="H8" s="30"/>
+      <c r="I8" s="30"/>
+      <c r="J8" s="30"/>
+      <c r="K8" s="30"/>
+      <c r="L8" s="30"/>
+      <c r="M8" s="30"/>
+      <c r="N8" s="30"/>
+      <c r="O8" s="30"/>
+      <c r="P8" s="30"/>
+      <c r="Q8" s="30"/>
+      <c r="R8" s="30"/>
+      <c r="S8" s="30"/>
+      <c r="T8" s="30"/>
+      <c r="U8" s="30"/>
+      <c r="V8" s="30"/>
+      <c r="W8" s="30"/>
+      <c r="X8" s="12"/>
+      <c r="Y8" s="12"/>
+      <c r="Z8" s="12"/>
+    </row>
+    <row r="9" spans="1:26" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9" s="29" t="s">
+        <v>29</v>
+      </c>
+      <c r="D9" s="29"/>
+      <c r="E9" s="29"/>
+      <c r="F9" s="29"/>
+      <c r="G9" s="29"/>
+      <c r="H9" s="29"/>
+      <c r="I9" s="29"/>
+      <c r="J9" s="29"/>
+      <c r="K9" s="29"/>
+      <c r="L9" s="29"/>
+      <c r="M9" s="29"/>
+      <c r="N9" s="29"/>
+      <c r="O9" s="29"/>
+      <c r="P9" s="29"/>
+      <c r="Q9" s="29"/>
+      <c r="R9" s="29"/>
+      <c r="S9" s="29"/>
+      <c r="T9" s="29"/>
+      <c r="U9" s="29"/>
+      <c r="V9" s="29"/>
+      <c r="W9" s="29"/>
+      <c r="X9" s="12"/>
+      <c r="Y9" s="12"/>
+      <c r="Z9" s="12"/>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="C10" s="14" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A11" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C11" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="D11" s="14"/>
+      <c r="E11" s="14"/>
+      <c r="F11" s="14"/>
+      <c r="G11" s="14"/>
+    </row>
+    <row r="13" spans="1:26" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="B13" s="22" t="s">
+        <v>35</v>
+      </c>
       <c r="C13" s="28" t="s">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="D13" s="28"/>
       <c r="E13" s="28"/>
@@ -1440,53 +1946,21 @@
       <c r="U13" s="28"/>
       <c r="V13" s="28"/>
       <c r="W13" s="28"/>
-      <c r="X13" s="28"/>
-      <c r="Y13" s="28"/>
-      <c r="Z13" s="7"/>
-    </row>
-    <row r="14" spans="1:27" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="B14" s="6">
-        <v>7</v>
-      </c>
-      <c r="C14" s="28" t="s">
-        <v>11</v>
-      </c>
-      <c r="D14" s="28"/>
-      <c r="E14" s="28"/>
-      <c r="F14" s="28"/>
-      <c r="G14" s="28"/>
-      <c r="H14" s="28"/>
-      <c r="I14" s="28"/>
-      <c r="J14" s="28"/>
-      <c r="K14" s="28"/>
-      <c r="L14" s="28"/>
-      <c r="M14" s="28"/>
-      <c r="N14" s="28"/>
-      <c r="O14" s="28"/>
-      <c r="P14" s="28"/>
-      <c r="Q14" s="28"/>
-      <c r="R14" s="28"/>
-      <c r="S14" s="28"/>
-      <c r="T14" s="28"/>
-      <c r="U14" s="28"/>
-      <c r="V14" s="28"/>
-      <c r="W14" s="28"/>
-      <c r="X14" s="28"/>
-      <c r="Y14" s="28"/>
-      <c r="Z14" s="7"/>
-    </row>
-    <row r="15" spans="1:27" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="B15" s="6">
-        <v>8</v>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="C14" s="16" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" ht="75.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>39</v>
       </c>
       <c r="C15" s="28" t="s">
-        <v>12</v>
+        <v>41</v>
       </c>
       <c r="D15" s="28"/>
       <c r="E15" s="28"/>
@@ -1508,52 +1982,21 @@
       <c r="U15" s="28"/>
       <c r="V15" s="28"/>
       <c r="W15" s="28"/>
-      <c r="X15" s="28"/>
-      <c r="Y15" s="28"/>
-      <c r="Z15" s="7"/>
-    </row>
-    <row r="16" spans="1:27" ht="48" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="B16" s="6">
-        <v>9</v>
-      </c>
-      <c r="C16" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="D16" s="28"/>
-      <c r="E16" s="28"/>
-      <c r="F16" s="28"/>
-      <c r="G16" s="28"/>
-      <c r="H16" s="28"/>
-      <c r="I16" s="28"/>
-      <c r="J16" s="28"/>
-      <c r="K16" s="28"/>
-      <c r="L16" s="28"/>
-      <c r="M16" s="28"/>
-      <c r="N16" s="28"/>
-      <c r="O16" s="28"/>
-      <c r="P16" s="28"/>
-      <c r="Q16" s="28"/>
-      <c r="R16" s="28"/>
-      <c r="S16" s="28"/>
-      <c r="T16" s="28"/>
-      <c r="U16" s="28"/>
-      <c r="V16" s="28"/>
-      <c r="W16" s="28"/>
-      <c r="X16" s="28"/>
-      <c r="Y16" s="28"/>
-    </row>
-    <row r="17" spans="1:25" ht="57.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="B17" s="6">
-        <v>10</v>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="C16" s="16" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="17" spans="1:23" ht="292.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>42</v>
       </c>
       <c r="C17" s="28" t="s">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="D17" s="28"/>
       <c r="E17" s="28"/>
@@ -1575,452 +2018,6 @@
       <c r="U17" s="28"/>
       <c r="V17" s="28"/>
       <c r="W17" s="28"/>
-      <c r="X17" s="28"/>
-      <c r="Y17" s="28"/>
-    </row>
-    <row r="18" spans="1:25" ht="48" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="B18" s="6">
-        <v>11</v>
-      </c>
-      <c r="C18" s="28" t="s">
-        <v>15</v>
-      </c>
-      <c r="D18" s="28"/>
-      <c r="E18" s="28"/>
-      <c r="F18" s="28"/>
-      <c r="G18" s="28"/>
-      <c r="H18" s="28"/>
-      <c r="I18" s="28"/>
-      <c r="J18" s="28"/>
-      <c r="K18" s="28"/>
-      <c r="L18" s="28"/>
-      <c r="M18" s="28"/>
-      <c r="N18" s="28"/>
-      <c r="O18" s="28"/>
-      <c r="P18" s="28"/>
-      <c r="Q18" s="28"/>
-      <c r="R18" s="28"/>
-      <c r="S18" s="28"/>
-      <c r="T18" s="28"/>
-      <c r="U18" s="28"/>
-      <c r="V18" s="28"/>
-      <c r="W18" s="28"/>
-      <c r="X18" s="28"/>
-      <c r="Y18" s="28"/>
-    </row>
-    <row r="19" spans="1:25" ht="55.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="B19" s="6">
-        <v>12</v>
-      </c>
-      <c r="C19" s="28" t="s">
-        <v>16</v>
-      </c>
-      <c r="D19" s="28"/>
-      <c r="E19" s="28"/>
-      <c r="F19" s="28"/>
-      <c r="G19" s="28"/>
-      <c r="H19" s="28"/>
-      <c r="I19" s="28"/>
-      <c r="J19" s="28"/>
-      <c r="K19" s="28"/>
-      <c r="L19" s="28"/>
-      <c r="M19" s="28"/>
-      <c r="N19" s="28"/>
-      <c r="O19" s="28"/>
-      <c r="P19" s="28"/>
-      <c r="Q19" s="28"/>
-      <c r="R19" s="28"/>
-      <c r="S19" s="28"/>
-      <c r="T19" s="28"/>
-      <c r="U19" s="28"/>
-      <c r="V19" s="28"/>
-      <c r="W19" s="28"/>
-      <c r="X19" s="28"/>
-      <c r="Y19" s="28"/>
-    </row>
-  </sheetData>
-  <mergeCells count="16">
-    <mergeCell ref="C17:Y17"/>
-    <mergeCell ref="C18:Y18"/>
-    <mergeCell ref="C19:Y19"/>
-    <mergeCell ref="C8:Y8"/>
-    <mergeCell ref="C9:Y9"/>
-    <mergeCell ref="C10:Y10"/>
-    <mergeCell ref="C11:Y11"/>
-    <mergeCell ref="C12:Y12"/>
-    <mergeCell ref="C13:Y13"/>
-    <mergeCell ref="C14:Y14"/>
-    <mergeCell ref="C15:Y15"/>
-    <mergeCell ref="A4:Z4"/>
-    <mergeCell ref="A5:Z5"/>
-    <mergeCell ref="A1:Z1"/>
-    <mergeCell ref="A3:Z3"/>
-    <mergeCell ref="C16:Y16"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E579CA94-23C4-4A08-ACCB-1F78709F95AA}">
-  <dimension ref="A1:Z32"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="35.7109375" customWidth="1"/>
-    <col min="2" max="2" width="18.7109375" customWidth="1"/>
-    <col min="3" max="3" width="14.5703125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:26" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A1" s="32" t="s">
-        <v>17</v>
-      </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="32"/>
-      <c r="F1" s="32"/>
-      <c r="G1" s="32"/>
-      <c r="H1" s="32"/>
-      <c r="I1" s="32"/>
-      <c r="J1" s="32"/>
-      <c r="K1" s="32"/>
-      <c r="L1" s="32"/>
-      <c r="M1" s="32"/>
-      <c r="N1" s="32"/>
-      <c r="O1" s="32"/>
-      <c r="P1" s="32"/>
-      <c r="Q1" s="32"/>
-      <c r="R1" s="32"/>
-      <c r="S1" s="32"/>
-      <c r="T1" s="32"/>
-      <c r="U1" s="32"/>
-      <c r="V1" s="32"/>
-      <c r="W1" s="32"/>
-      <c r="X1" s="32"/>
-      <c r="Y1" s="32"/>
-      <c r="Z1" s="32"/>
-    </row>
-    <row r="3" spans="1:26" ht="52.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="33" t="s">
-        <v>18</v>
-      </c>
-      <c r="B3" s="33"/>
-      <c r="C3" s="33"/>
-      <c r="D3" s="33"/>
-      <c r="E3" s="33"/>
-      <c r="F3" s="33"/>
-      <c r="G3" s="33"/>
-      <c r="H3" s="33"/>
-      <c r="I3" s="33"/>
-      <c r="J3" s="33"/>
-      <c r="K3" s="33"/>
-      <c r="L3" s="33"/>
-      <c r="M3" s="33"/>
-      <c r="N3" s="33"/>
-      <c r="O3" s="33"/>
-      <c r="P3" s="33"/>
-      <c r="Q3" s="33"/>
-      <c r="R3" s="33"/>
-      <c r="S3" s="33"/>
-      <c r="T3" s="33"/>
-      <c r="U3" s="33"/>
-      <c r="V3" s="33"/>
-      <c r="W3" s="33"/>
-      <c r="X3" s="33"/>
-      <c r="Y3" s="33"/>
-      <c r="Z3" s="33"/>
-    </row>
-    <row r="4" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="33" t="s">
-        <v>19</v>
-      </c>
-      <c r="B4" s="33"/>
-      <c r="C4" s="33"/>
-      <c r="D4" s="33"/>
-      <c r="E4" s="33"/>
-      <c r="F4" s="33"/>
-      <c r="G4" s="33"/>
-      <c r="H4" s="33"/>
-      <c r="I4" s="33"/>
-      <c r="J4" s="33"/>
-      <c r="K4" s="33"/>
-      <c r="L4" s="33"/>
-      <c r="M4" s="33"/>
-      <c r="N4" s="33"/>
-      <c r="O4" s="33"/>
-      <c r="P4" s="33"/>
-      <c r="Q4" s="33"/>
-      <c r="R4" s="33"/>
-      <c r="S4" s="33"/>
-      <c r="T4" s="33"/>
-      <c r="U4" s="33"/>
-      <c r="V4" s="33"/>
-      <c r="W4" s="33"/>
-      <c r="X4" s="33"/>
-      <c r="Y4" s="33"/>
-      <c r="Z4" s="33"/>
-    </row>
-    <row r="5" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="33" t="s">
-        <v>20</v>
-      </c>
-      <c r="B5" s="33"/>
-      <c r="C5" s="33"/>
-      <c r="D5" s="33"/>
-      <c r="E5" s="33"/>
-      <c r="F5" s="33"/>
-      <c r="G5" s="33"/>
-      <c r="H5" s="33"/>
-      <c r="I5" s="33"/>
-      <c r="J5" s="33"/>
-      <c r="K5" s="33"/>
-      <c r="L5" s="33"/>
-      <c r="M5" s="33"/>
-      <c r="N5" s="33"/>
-      <c r="O5" s="33"/>
-      <c r="P5" s="33"/>
-      <c r="Q5" s="33"/>
-      <c r="R5" s="33"/>
-      <c r="S5" s="33"/>
-      <c r="T5" s="33"/>
-      <c r="U5" s="33"/>
-      <c r="V5" s="33"/>
-      <c r="W5" s="33"/>
-      <c r="X5" s="33"/>
-      <c r="Y5" s="33"/>
-      <c r="Z5" s="33"/>
-    </row>
-    <row r="7" spans="1:26" ht="59.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" s="17" t="s">
-        <v>24</v>
-      </c>
-      <c r="C7" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="D7" s="31"/>
-      <c r="E7" s="31"/>
-      <c r="F7" s="31"/>
-      <c r="G7" s="31"/>
-      <c r="H7" s="31"/>
-      <c r="I7" s="31"/>
-      <c r="J7" s="31"/>
-      <c r="K7" s="31"/>
-      <c r="L7" s="31"/>
-      <c r="M7" s="31"/>
-      <c r="N7" s="31"/>
-      <c r="O7" s="31"/>
-      <c r="P7" s="31"/>
-      <c r="Q7" s="31"/>
-      <c r="R7" s="31"/>
-      <c r="S7" s="31"/>
-      <c r="T7" s="31"/>
-      <c r="U7" s="31"/>
-      <c r="V7" s="31"/>
-      <c r="W7" s="31"/>
-      <c r="X7" s="12"/>
-      <c r="Y7" s="12"/>
-      <c r="Z7" s="12"/>
-    </row>
-    <row r="8" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C8" s="31" t="s">
-        <v>27</v>
-      </c>
-      <c r="D8" s="31"/>
-      <c r="E8" s="31"/>
-      <c r="F8" s="31"/>
-      <c r="G8" s="31"/>
-      <c r="H8" s="31"/>
-      <c r="I8" s="31"/>
-      <c r="J8" s="31"/>
-      <c r="K8" s="31"/>
-      <c r="L8" s="31"/>
-      <c r="M8" s="31"/>
-      <c r="N8" s="31"/>
-      <c r="O8" s="31"/>
-      <c r="P8" s="31"/>
-      <c r="Q8" s="31"/>
-      <c r="R8" s="31"/>
-      <c r="S8" s="31"/>
-      <c r="T8" s="31"/>
-      <c r="U8" s="31"/>
-      <c r="V8" s="31"/>
-      <c r="W8" s="31"/>
-      <c r="X8" s="12"/>
-      <c r="Y8" s="12"/>
-      <c r="Z8" s="12"/>
-    </row>
-    <row r="9" spans="1:26" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="C9" s="30" t="s">
-        <v>29</v>
-      </c>
-      <c r="D9" s="30"/>
-      <c r="E9" s="30"/>
-      <c r="F9" s="30"/>
-      <c r="G9" s="30"/>
-      <c r="H9" s="30"/>
-      <c r="I9" s="30"/>
-      <c r="J9" s="30"/>
-      <c r="K9" s="30"/>
-      <c r="L9" s="30"/>
-      <c r="M9" s="30"/>
-      <c r="N9" s="30"/>
-      <c r="O9" s="30"/>
-      <c r="P9" s="30"/>
-      <c r="Q9" s="30"/>
-      <c r="R9" s="30"/>
-      <c r="S9" s="30"/>
-      <c r="T9" s="30"/>
-      <c r="U9" s="30"/>
-      <c r="V9" s="30"/>
-      <c r="W9" s="30"/>
-      <c r="X9" s="12"/>
-      <c r="Y9" s="12"/>
-      <c r="Z9" s="12"/>
-    </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="C10" s="14" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A11" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="C11" s="14" t="s">
-        <v>32</v>
-      </c>
-      <c r="D11" s="14"/>
-      <c r="E11" s="14"/>
-      <c r="F11" s="14"/>
-      <c r="G11" s="14"/>
-    </row>
-    <row r="13" spans="1:26" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="19" t="s">
-        <v>34</v>
-      </c>
-      <c r="B13" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="C13" s="29" t="s">
-        <v>36</v>
-      </c>
-      <c r="D13" s="29"/>
-      <c r="E13" s="29"/>
-      <c r="F13" s="29"/>
-      <c r="G13" s="29"/>
-      <c r="H13" s="29"/>
-      <c r="I13" s="29"/>
-      <c r="J13" s="29"/>
-      <c r="K13" s="29"/>
-      <c r="L13" s="29"/>
-      <c r="M13" s="29"/>
-      <c r="N13" s="29"/>
-      <c r="O13" s="29"/>
-      <c r="P13" s="29"/>
-      <c r="Q13" s="29"/>
-      <c r="R13" s="29"/>
-      <c r="S13" s="29"/>
-      <c r="T13" s="29"/>
-      <c r="U13" s="29"/>
-      <c r="V13" s="29"/>
-      <c r="W13" s="29"/>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="C14" s="16" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="15" spans="1:26" ht="75.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="C15" s="29" t="s">
-        <v>41</v>
-      </c>
-      <c r="D15" s="29"/>
-      <c r="E15" s="29"/>
-      <c r="F15" s="29"/>
-      <c r="G15" s="29"/>
-      <c r="H15" s="29"/>
-      <c r="I15" s="29"/>
-      <c r="J15" s="29"/>
-      <c r="K15" s="29"/>
-      <c r="L15" s="29"/>
-      <c r="M15" s="29"/>
-      <c r="N15" s="29"/>
-      <c r="O15" s="29"/>
-      <c r="P15" s="29"/>
-      <c r="Q15" s="29"/>
-      <c r="R15" s="29"/>
-      <c r="S15" s="29"/>
-      <c r="T15" s="29"/>
-      <c r="U15" s="29"/>
-      <c r="V15" s="29"/>
-      <c r="W15" s="29"/>
-    </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="C16" s="16" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="17" spans="1:23" ht="292.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="C17" s="29" t="s">
-        <v>45</v>
-      </c>
-      <c r="D17" s="29"/>
-      <c r="E17" s="29"/>
-      <c r="F17" s="29"/>
-      <c r="G17" s="29"/>
-      <c r="H17" s="29"/>
-      <c r="I17" s="29"/>
-      <c r="J17" s="29"/>
-      <c r="K17" s="29"/>
-      <c r="L17" s="29"/>
-      <c r="M17" s="29"/>
-      <c r="N17" s="29"/>
-      <c r="O17" s="29"/>
-      <c r="P17" s="29"/>
-      <c r="Q17" s="29"/>
-      <c r="R17" s="29"/>
-      <c r="S17" s="29"/>
-      <c r="T17" s="29"/>
-      <c r="U17" s="29"/>
-      <c r="V17" s="29"/>
-      <c r="W17" s="29"/>
     </row>
     <row r="18" spans="1:23" x14ac:dyDescent="0.25">
       <c r="C18" t="s">
@@ -2045,29 +2042,29 @@
       <c r="B21" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="C21" s="29" t="s">
+      <c r="C21" s="28" t="s">
         <v>50</v>
       </c>
-      <c r="D21" s="29"/>
-      <c r="E21" s="29"/>
-      <c r="F21" s="29"/>
-      <c r="G21" s="29"/>
-      <c r="H21" s="29"/>
-      <c r="I21" s="29"/>
-      <c r="J21" s="29"/>
-      <c r="K21" s="29"/>
-      <c r="L21" s="29"/>
-      <c r="M21" s="29"/>
-      <c r="N21" s="29"/>
-      <c r="O21" s="29"/>
-      <c r="P21" s="29"/>
-      <c r="Q21" s="29"/>
-      <c r="R21" s="29"/>
-      <c r="S21" s="29"/>
-      <c r="T21" s="29"/>
-      <c r="U21" s="29"/>
-      <c r="V21" s="29"/>
-      <c r="W21" s="29"/>
+      <c r="D21" s="28"/>
+      <c r="E21" s="28"/>
+      <c r="F21" s="28"/>
+      <c r="G21" s="28"/>
+      <c r="H21" s="28"/>
+      <c r="I21" s="28"/>
+      <c r="J21" s="28"/>
+      <c r="K21" s="28"/>
+      <c r="L21" s="28"/>
+      <c r="M21" s="28"/>
+      <c r="N21" s="28"/>
+      <c r="O21" s="28"/>
+      <c r="P21" s="28"/>
+      <c r="Q21" s="28"/>
+      <c r="R21" s="28"/>
+      <c r="S21" s="28"/>
+      <c r="T21" s="28"/>
+      <c r="U21" s="28"/>
+      <c r="V21" s="28"/>
+      <c r="W21" s="28"/>
     </row>
     <row r="22" spans="1:23" x14ac:dyDescent="0.25">
       <c r="C22" s="16" t="s">
@@ -2081,29 +2078,29 @@
       <c r="B23" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="C23" s="29" t="s">
+      <c r="C23" s="28" t="s">
         <v>54</v>
       </c>
-      <c r="D23" s="29"/>
-      <c r="E23" s="29"/>
-      <c r="F23" s="29"/>
-      <c r="G23" s="29"/>
-      <c r="H23" s="29"/>
-      <c r="I23" s="29"/>
-      <c r="J23" s="29"/>
-      <c r="K23" s="29"/>
-      <c r="L23" s="29"/>
-      <c r="M23" s="29"/>
-      <c r="N23" s="29"/>
-      <c r="O23" s="29"/>
-      <c r="P23" s="29"/>
-      <c r="Q23" s="29"/>
-      <c r="R23" s="29"/>
-      <c r="S23" s="29"/>
-      <c r="T23" s="29"/>
-      <c r="U23" s="29"/>
-      <c r="V23" s="29"/>
-      <c r="W23" s="29"/>
+      <c r="D23" s="28"/>
+      <c r="E23" s="28"/>
+      <c r="F23" s="28"/>
+      <c r="G23" s="28"/>
+      <c r="H23" s="28"/>
+      <c r="I23" s="28"/>
+      <c r="J23" s="28"/>
+      <c r="K23" s="28"/>
+      <c r="L23" s="28"/>
+      <c r="M23" s="28"/>
+      <c r="N23" s="28"/>
+      <c r="O23" s="28"/>
+      <c r="P23" s="28"/>
+      <c r="Q23" s="28"/>
+      <c r="R23" s="28"/>
+      <c r="S23" s="28"/>
+      <c r="T23" s="28"/>
+      <c r="U23" s="28"/>
+      <c r="V23" s="28"/>
+      <c r="W23" s="28"/>
     </row>
     <row r="24" spans="1:23" ht="160.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="18" t="s">
@@ -2112,29 +2109,29 @@
       <c r="B24" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="C24" s="29" t="s">
+      <c r="C24" s="28" t="s">
         <v>57</v>
       </c>
-      <c r="D24" s="29"/>
-      <c r="E24" s="29"/>
-      <c r="F24" s="29"/>
-      <c r="G24" s="29"/>
-      <c r="H24" s="29"/>
-      <c r="I24" s="29"/>
-      <c r="J24" s="29"/>
-      <c r="K24" s="29"/>
-      <c r="L24" s="29"/>
-      <c r="M24" s="29"/>
-      <c r="N24" s="29"/>
-      <c r="O24" s="29"/>
-      <c r="P24" s="29"/>
-      <c r="Q24" s="29"/>
-      <c r="R24" s="29"/>
-      <c r="S24" s="29"/>
-      <c r="T24" s="29"/>
-      <c r="U24" s="29"/>
-      <c r="V24" s="29"/>
-      <c r="W24" s="29"/>
+      <c r="D24" s="28"/>
+      <c r="E24" s="28"/>
+      <c r="F24" s="28"/>
+      <c r="G24" s="28"/>
+      <c r="H24" s="28"/>
+      <c r="I24" s="28"/>
+      <c r="J24" s="28"/>
+      <c r="K24" s="28"/>
+      <c r="L24" s="28"/>
+      <c r="M24" s="28"/>
+      <c r="N24" s="28"/>
+      <c r="O24" s="28"/>
+      <c r="P24" s="28"/>
+      <c r="Q24" s="28"/>
+      <c r="R24" s="28"/>
+      <c r="S24" s="28"/>
+      <c r="T24" s="28"/>
+      <c r="U24" s="28"/>
+      <c r="V24" s="28"/>
+      <c r="W24" s="28"/>
     </row>
     <row r="25" spans="1:23" x14ac:dyDescent="0.25">
       <c r="C25" s="16" t="s">
@@ -2156,7 +2153,7 @@
       <c r="A28" s="20" t="s">
         <v>61</v>
       </c>
-      <c r="B28" s="22" t="s">
+      <c r="B28" s="3" t="s">
         <v>62</v>
       </c>
       <c r="C28" s="16" t="s">
@@ -2178,7 +2175,7 @@
       <c r="A31" s="18" t="s">
         <v>66</v>
       </c>
-      <c r="B31" s="3" t="s">
+      <c r="B31" s="22" t="s">
         <v>67</v>
       </c>
       <c r="C31" s="16" t="s">
@@ -2198,11 +2195,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="C15:W15"/>
-    <mergeCell ref="C17:W17"/>
-    <mergeCell ref="C21:W21"/>
-    <mergeCell ref="C23:W23"/>
-    <mergeCell ref="C24:W24"/>
     <mergeCell ref="C13:W13"/>
     <mergeCell ref="C9:W9"/>
     <mergeCell ref="C8:W8"/>
@@ -2211,6 +2203,11 @@
     <mergeCell ref="A4:Z4"/>
     <mergeCell ref="A5:Z5"/>
     <mergeCell ref="C7:W7"/>
+    <mergeCell ref="C15:W15"/>
+    <mergeCell ref="C17:W17"/>
+    <mergeCell ref="C21:W21"/>
+    <mergeCell ref="C23:W23"/>
+    <mergeCell ref="C24:W24"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="C10" r:id="rId1" xr:uid="{E87D090F-0661-4714-B69F-526E634EDD35}"/>
@@ -2240,55 +2237,55 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="31" t="s">
         <v>72</v>
       </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="32"/>
-      <c r="F1" s="32"/>
-      <c r="G1" s="32"/>
-      <c r="H1" s="32"/>
-      <c r="I1" s="32"/>
-      <c r="J1" s="32"/>
-      <c r="K1" s="32"/>
-      <c r="L1" s="32"/>
-      <c r="M1" s="32"/>
-      <c r="N1" s="32"/>
-      <c r="O1" s="32"/>
-      <c r="P1" s="32"/>
-      <c r="Q1" s="32"/>
-      <c r="R1" s="32"/>
-      <c r="S1" s="32"/>
-      <c r="T1" s="32"/>
-      <c r="U1" s="32"/>
-      <c r="V1" s="32"/>
-      <c r="W1" s="32"/>
-      <c r="X1" s="32"/>
-      <c r="Y1" s="32"/>
-      <c r="Z1" s="32"/>
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="31"/>
+      <c r="H1" s="31"/>
+      <c r="I1" s="31"/>
+      <c r="J1" s="31"/>
+      <c r="K1" s="31"/>
+      <c r="L1" s="31"/>
+      <c r="M1" s="31"/>
+      <c r="N1" s="31"/>
+      <c r="O1" s="31"/>
+      <c r="P1" s="31"/>
+      <c r="Q1" s="31"/>
+      <c r="R1" s="31"/>
+      <c r="S1" s="31"/>
+      <c r="T1" s="31"/>
+      <c r="U1" s="31"/>
+      <c r="V1" s="31"/>
+      <c r="W1" s="31"/>
+      <c r="X1" s="31"/>
+      <c r="Y1" s="31"/>
+      <c r="Z1" s="31"/>
     </row>
     <row r="2" spans="1:26" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="33" t="s">
+      <c r="A2" s="32" t="s">
         <v>73</v>
       </c>
-      <c r="B2" s="33"/>
-      <c r="C2" s="33"/>
-      <c r="D2" s="33"/>
-      <c r="E2" s="33"/>
-      <c r="F2" s="33"/>
-      <c r="G2" s="33"/>
-      <c r="H2" s="33"/>
-      <c r="I2" s="33"/>
-      <c r="J2" s="33"/>
-      <c r="K2" s="33"/>
-      <c r="L2" s="33"/>
-      <c r="M2" s="33"/>
-      <c r="N2" s="33"/>
-      <c r="O2" s="33"/>
-      <c r="P2" s="33"/>
-      <c r="Q2" s="33"/>
+      <c r="B2" s="32"/>
+      <c r="C2" s="32"/>
+      <c r="D2" s="32"/>
+      <c r="E2" s="32"/>
+      <c r="F2" s="32"/>
+      <c r="G2" s="32"/>
+      <c r="H2" s="32"/>
+      <c r="I2" s="32"/>
+      <c r="J2" s="32"/>
+      <c r="K2" s="32"/>
+      <c r="L2" s="32"/>
+      <c r="M2" s="32"/>
+      <c r="N2" s="32"/>
+      <c r="O2" s="32"/>
+      <c r="P2" s="32"/>
+      <c r="Q2" s="32"/>
       <c r="R2" s="1"/>
       <c r="S2" s="1"/>
       <c r="T2" s="1"/>
@@ -2392,24 +2389,24 @@
       <c r="Z7" s="1"/>
     </row>
     <row r="8" spans="1:26" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="33" t="s">
+      <c r="A8" s="32" t="s">
         <v>77</v>
       </c>
-      <c r="B8" s="33"/>
-      <c r="C8" s="33"/>
-      <c r="D8" s="33"/>
-      <c r="E8" s="33"/>
-      <c r="F8" s="33"/>
-      <c r="G8" s="33"/>
-      <c r="H8" s="33"/>
-      <c r="I8" s="33"/>
-      <c r="J8" s="33"/>
-      <c r="K8" s="33"/>
-      <c r="L8" s="33"/>
-      <c r="M8" s="33"/>
-      <c r="N8" s="33"/>
-      <c r="O8" s="33"/>
-      <c r="P8" s="33"/>
+      <c r="B8" s="32"/>
+      <c r="C8" s="32"/>
+      <c r="D8" s="32"/>
+      <c r="E8" s="32"/>
+      <c r="F8" s="32"/>
+      <c r="G8" s="32"/>
+      <c r="H8" s="32"/>
+      <c r="I8" s="32"/>
+      <c r="J8" s="32"/>
+      <c r="K8" s="32"/>
+      <c r="L8" s="32"/>
+      <c r="M8" s="32"/>
+      <c r="N8" s="32"/>
+      <c r="O8" s="32"/>
+      <c r="P8" s="32"/>
       <c r="Q8" s="1"/>
       <c r="R8" s="1"/>
       <c r="S8" s="1"/>
@@ -2531,7 +2528,7 @@
       <c r="A15" s="15" t="s">
         <v>81</v>
       </c>
-      <c r="B15" s="23" t="s">
+      <c r="B15" s="17" t="s">
         <v>85</v>
       </c>
     </row>
@@ -2576,7 +2573,7 @@
       <c r="A21" s="20" t="s">
         <v>88</v>
       </c>
-      <c r="B21" s="21" t="s">
+      <c r="B21" s="23" t="s">
         <v>93</v>
       </c>
     </row>
@@ -2584,7 +2581,7 @@
       <c r="A22" s="20" t="s">
         <v>88</v>
       </c>
-      <c r="B22" s="24" t="s">
+      <c r="B22" s="23" t="s">
         <v>91</v>
       </c>
     </row>
@@ -2592,7 +2589,7 @@
       <c r="A23" s="20" t="s">
         <v>88</v>
       </c>
-      <c r="B23" s="25" t="s">
+      <c r="B23" s="24" t="s">
         <v>92</v>
       </c>
     </row>
